--- a/data/production/production_2026-W38.xlsx
+++ b/data/production/production_2026-W38.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -483,33 +483,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Luis Ortega</t>
+          <t>grant fowler</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LF-308727</t>
+          <t>HO-500664</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Grace Delgado</t>
+          <t>Sofia Marsh</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Renewal</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>$2,095.89</t>
-        </is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>2568.36</v>
       </c>
     </row>
     <row r="5">
@@ -523,28 +521,26 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AU-553633</t>
+          <t>AU-476868</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Leah Novak</t>
+          <t>Olivia Hartley</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Renewal</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>$2,584.88</t>
-        </is>
+          <t>renewal</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1451.4</v>
       </c>
     </row>
     <row r="6">
@@ -553,31 +549,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Priya Raman</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CM-955374</t>
+          <t>AU-509306</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Leah Okafor</t>
+          <t>Alma Ashby</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Commercial</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>New</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4536.22</v>
+        <v>1278.06</v>
       </c>
     </row>
     <row r="7">
@@ -586,17 +582,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Priya Raman </t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HO-913864</t>
+          <t>HO-679295</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Hugo Kowal</t>
+          <t>Maria Novak</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -609,41 +605,43 @@
           <t>Renewal</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>2486.97</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>$1,321.92</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HO-594514</t>
+          <t>LF-838382</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Caleb Whitfield</t>
+          <t>Maria Novak</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>New</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2946.66</v>
+        <v>628.1799999999999</v>
       </c>
     </row>
     <row r="9">
@@ -652,31 +650,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Grant Fowler</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AU-111991</t>
+          <t>HO-279101</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Samuel Brennan</t>
+          <t>Elena Novak</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>New</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2031.81</v>
+        <v>1830.21</v>
       </c>
     </row>
     <row r="10">
@@ -685,22 +683,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Grant Fowler</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AU-601410</t>
+          <t>HO-296780</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Maria Novak</t>
+          <t>Maria Moreau</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -709,7 +707,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1231.27</v>
+        <v>2088.88</v>
       </c>
     </row>
     <row r="11">
@@ -718,33 +716,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Luis Ortega</t>
+          <t>Priya Raman</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AU-443897</t>
+          <t>CM-994530</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mila Novak</t>
+          <t>Elena Mbeki</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>$2,239.70</t>
-        </is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>8154.17</v>
       </c>
     </row>
     <row r="12">
@@ -753,22 +749,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AU-486831</t>
+          <t>LF-806106</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mila Novak</t>
+          <t>Leah Okafor</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -777,31 +773,31 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1934.34</v>
+        <v>1183.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Luis Ortega</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HO-906527</t>
+          <t>CM-310690</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Victor Castillo</t>
+          <t>Samuel Brennan</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -809,27 +805,29 @@
           <t>Renewal</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>2327.9</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>$6,276.65</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Priya Raman</t>
+          <t>Luis Ortega</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CM-856215</t>
+          <t>CM-416202</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Felix Tanaka</t>
+          <t>Clara Pryor</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -842,34 +840,32 @@
           <t>Renewal</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>$6,475.67</t>
-        </is>
+      <c r="G14" t="n">
+        <v>7640.87</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>Luis Ortega</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>HO-794395</t>
+          <t>HO-700679</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Grace Albright</t>
+          <t>Olivia Delgado</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Home</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -878,7 +874,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2338.28</v>
+        <v>2951.98</v>
       </c>
     </row>
     <row r="16">
@@ -887,17 +883,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>priya raman</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CM-823769</t>
+          <t>CM-145000</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Lena Quill</t>
+          <t>Nora Ruiz</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -907,11 +903,11 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t xml:space="preserve">Renewal </t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>7206.19</v>
+        <v>8753.450000000001</v>
       </c>
     </row>
     <row r="17">
@@ -920,17 +916,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Grant Fowler</t>
+          <t>Priya Raman</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HO-267475</t>
+          <t>HO-331328</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Elena Mbeki</t>
+          <t>Grace Albright</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -940,11 +936,11 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t xml:space="preserve"> Renewal</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2171.6</v>
+        <v>2073.86</v>
       </c>
     </row>
     <row r="18">
@@ -953,22 +949,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Luis Ortega</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AU-505116</t>
+          <t>HO-539272</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Mila Novak</t>
+          <t>Ruby Ferreira</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -977,34 +973,64 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1445.74</v>
+        <v>2863.36</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n"/>
+      <c r="A19" s="2" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Tom Becker</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>LF-582140</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Hannah Haines</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>2074.82</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Luis Ortega</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HO-201377</t>
+          <t>CM-306196</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Lena Quill</t>
+          <t>Owen Kowal</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Home</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1012,32 +1038,34 @@
           <t>Renewal</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>1469.92</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>$9,127.81</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AU-843788</t>
+          <t>LF-340975</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ivy Hartley</t>
+          <t>Ruby Sorensen</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1046,26 +1074,26 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1146.99</v>
+        <v>707.41</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Grant Fowler</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AU-987025</t>
+          <t>AU-523078</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Theo Moreau</t>
+          <t>James Whitfield</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1075,137 +1103,169 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>2311.36</v>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>$1,345.89</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HO-744274</t>
+          <t>LF-452467</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Felix Lindqvist</t>
+          <t>Hannah Haines</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Renewal</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1362.86</v>
+        <v>2036.56</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HO-685196</t>
+          <t>HO-685157</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Maria Duarte</t>
+          <t>Owen Sorensen</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t xml:space="preserve">Home </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>1345.14</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>grant fowler</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>HO-571577</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Maria Lopez</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>New</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>3110.41</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n"/>
+      <c r="G25" t="n">
+        <v>2193.93</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LF-471496</t>
+          <t>HO-176711</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Mila Novak</t>
+          <t>Adrian Okafor</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>New</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1375.65</v>
+        <v>1333.57</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Luis Ortega</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AU-644559</t>
+          <t>LF-151606</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Grace Albright</t>
+          <t>Marcus Novak</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1214,41 +1274,11 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1970.39</v>
+        <v>2116.8</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>46282</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Priya Raman</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>AU-215233</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Maria Novak</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Auto</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Renewal</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>2406.27</v>
-      </c>
+      <c r="A28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -1256,22 +1286,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AU-350905</t>
+          <t>LF-241870</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Felix Tanaka</t>
+          <t>Grace Albright</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1280,41 +1310,11 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1063.84</v>
+        <v>1500.04</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>46283</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Aisha Bello</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>LF-386741</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Zoe Marsh</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Life</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Renewal</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>2229.55</v>
-      </c>
+      <c r="A30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GRANT FOWLER</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LF-257131</t>
+          <t>LF-235797</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1342,124 +1342,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>New</t>
+          <t xml:space="preserve"> Renewal</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>984.1</v>
+        <v>1620.97</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>46283</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Luis Ortega</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>AU-875232</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Maria Duarte</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Auto</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>1489.43</v>
-      </c>
+      <c r="A32" s="2" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>46283</v>
-      </c>
+      <c r="A33" s="2" t="n"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>HO-813145</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Hugo Kowal</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Renewal</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2022.97</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>46283</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Priya Raman </t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>CM-860557</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>James Moreau</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Renewal</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>8173.35</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n"/>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>75170.21000000001</v>
+        <v>76467.69</v>
       </c>
     </row>
   </sheetData>
@@ -1473,7 +1374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1511,7 +1412,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AU-486831</t>
+          <t>AU-476868</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1520,7 +1421,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1731.03</v>
+        <v>1479.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1536,41 +1437,41 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CM-517500</t>
+          <t>HO-679295</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2927.36</v>
+        <v>1294.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lost</t>
+          <t>Renewed</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Luis Ortega</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HO-906527</t>
+          <t>CM-416202</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2203.96</v>
+        <v>7057.62</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1581,21 +1482,21 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Luis Ortega</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HO-813145</t>
+          <t>CM-310690</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2044.95</v>
+        <v>6115.29</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1606,21 +1507,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Luis Ortega</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AU-553633</t>
+          <t>HO-700679</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2349.4</v>
+        <v>2650.76</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1631,21 +1532,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Luis Ortega</t>
+          <t>Priya Raman</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AU-505116</t>
+          <t>CM-994530</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1332.9</v>
+        <v>7747.52</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1656,12 +1557,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Luis Ortega</t>
+          <t>Priya Raman</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HO-201377</t>
+          <t>HO-331328</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1670,7 +1571,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1349.5</v>
+        <v>2065.96</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1681,21 +1582,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Luis Ortega</t>
+          <t>Priya Raman</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LF-308727</t>
+          <t>CM-145000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2034.43</v>
+        <v>7970.94</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1706,21 +1607,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Priya Raman</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CM-955374</t>
+          <t>LF-452467</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4448.64</v>
+        <v>2077.92</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1731,21 +1632,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Priya Raman</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CM-860557</t>
+          <t>HO-539272</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7678.91</v>
+        <v>2663.96</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1756,21 +1657,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Priya Raman</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HO-913864</t>
+          <t>LF-235797</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2476.74</v>
+        <v>1590.99</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1781,21 +1682,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Priya Raman</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CM-856215</t>
+          <t>LF-806106</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>5907.51</v>
+        <v>1103.99</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1806,21 +1707,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Priya Raman</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AU-215233</t>
+          <t>CM-306196</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2322.31</v>
+        <v>8328.59</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1831,12 +1732,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HO-594514</t>
+          <t>HO-685157</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1845,7 +1746,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2727.44</v>
+        <v>1358.31</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1856,198 +1757,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>Grant Fowler</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HO-794395</t>
+          <t>AU-523078</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2277.86</v>
+        <v>1341.13</v>
       </c>
       <c r="E16" t="inlineStr">
-        <is>
-          <t>Renewed</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Tom Becker</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>LF-471496</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Life</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>1250.42</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Renewed</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Aisha Bello</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>CM-823769</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>7081.86</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Renewed</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Aisha Bello</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>LF-386741</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Life</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>2111.27</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Renewed</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Aisha Bello</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>LF-461899</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Life</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>1349.61</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Lost</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Aisha Bello</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>LF-401602</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Life</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>1151.86</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Lost</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Grant Fowler</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>AU-111991</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Auto</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>1984.32</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Renewed</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Grant Fowler</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>HO-267475</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>2077.33</v>
-      </c>
-      <c r="E23" t="inlineStr">
         <is>
           <t>Renewed</t>
         </is>
